--- a/excel-importer/src/test/resources/CCD_TestDefinition_V12_FixedList_CaseType.xlsx
+++ b/excel-importer/src/test/resources/CCD_TestDefinition_V12_FixedList_CaseType.xlsx
@@ -16250,7 +16250,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="66" t="s">
         <v>85</v>
@@ -16290,7 +16290,7 @@
         <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="66" t="s">
         <v>87</v>
@@ -16330,7 +16330,7 @@
         <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="66" t="s">
         <v>89</v>
@@ -16370,7 +16370,7 @@
         <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="66" t="s">
         <v>91</v>
@@ -16410,7 +16410,7 @@
         <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="66" t="s">
         <v>93</v>
@@ -16450,7 +16450,7 @@
         <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" s="66" t="s">
         <v>95</v>
@@ -16490,7 +16490,7 @@
         <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="66" t="s">
         <v>97</v>
@@ -16530,7 +16530,7 @@
         <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" s="66" t="s">
         <v>261</v>
@@ -16570,7 +16570,7 @@
         <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="66" t="s">
         <v>262</v>
@@ -16610,7 +16610,7 @@
         <v>259</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" s="66" t="s">
         <v>261</v>
@@ -16650,7 +16650,7 @@
         <v>259</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" s="66" t="s">
         <v>262</v>
@@ -16690,7 +16690,7 @@
         <v>260</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="66" t="s">
         <v>261</v>
@@ -16730,7 +16730,7 @@
         <v>260</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" s="66" t="s">
         <v>262</v>
